--- a/האגמית7_כספים_2026.xlsx
+++ b/האגמית7_כספים_2026.xlsx
@@ -2480,7 +2480,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -2634,7 +2634,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2674,7 +2674,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2740,7 +2740,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -3452,14 +3452,30 @@
       <c r="H2" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I2" s="62" t="n"/>
-      <c r="J2" s="62" t="n"/>
-      <c r="K2" s="62" t="n"/>
-      <c r="L2" s="62" t="n"/>
-      <c r="M2" s="62" t="n"/>
-      <c r="N2" s="62" t="n"/>
-      <c r="O2" s="62" t="n"/>
-      <c r="P2" s="63" t="n"/>
+      <c r="I2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>250</v>
       </c>
@@ -3492,7 +3508,33 @@
       <c r="G3" t="n">
         <v>350</v>
       </c>
-      <c r="P3" s="46" t="n"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X3">
         <f t="array" ref="X3">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B3, _xlpm.payments, E3:P3, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -3520,8 +3562,30 @@
       <c r="H4" t="n">
         <v>350</v>
       </c>
-      <c r="O4" s="50" t="n"/>
-      <c r="P4" s="46" t="n"/>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>500</v>
       </c>
@@ -3555,14 +3619,30 @@
       <c r="H5" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I5" s="62" t="n"/>
-      <c r="J5" s="62" t="n"/>
-      <c r="K5" s="62" t="n"/>
-      <c r="L5" s="62" t="n"/>
-      <c r="M5" s="62" t="n"/>
-      <c r="N5" s="62" t="n"/>
-      <c r="O5" s="63" t="n"/>
-      <c r="P5" s="63" t="n"/>
+      <c r="I5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" s="62" t="n"/>
       <c r="X5">
         <f t="array" ref="X5">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B5, _xlpm.payments, E5:P5, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
@@ -3596,7 +3676,30 @@
       <c r="H6" t="n">
         <v>350</v>
       </c>
-      <c r="P6" s="46" t="n"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>500</v>
       </c>
@@ -3634,7 +3737,30 @@
       <c r="H7" t="n">
         <v>350</v>
       </c>
-      <c r="P7" s="46" t="n"/>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>500</v>
       </c>
@@ -3668,7 +3794,30 @@
       <c r="H8" t="n">
         <v>350</v>
       </c>
-      <c r="P8" s="46" t="n"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>500</v>
       </c>
@@ -3699,8 +3848,30 @@
       <c r="H9" t="n">
         <v>350</v>
       </c>
-      <c r="O9" s="46" t="n"/>
-      <c r="P9" s="46" t="n"/>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9">
         <f t="array" ref="X9">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B9, _xlpm.payments, E9:P9, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -3731,14 +3902,30 @@
       <c r="H10" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I10" s="62" t="n"/>
-      <c r="J10" s="62" t="n"/>
-      <c r="K10" s="62" t="n"/>
-      <c r="L10" s="62" t="n"/>
-      <c r="M10" s="62" t="n"/>
-      <c r="N10" s="62" t="n"/>
-      <c r="O10" s="62" t="n"/>
-      <c r="P10" s="63" t="n"/>
+      <c r="I10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="S10" s="62" t="n"/>
       <c r="X10">
         <f t="array" ref="X10">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B10, _xlpm.payments, E10:P10, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
@@ -3767,7 +3954,30 @@
       <c r="H11" t="n">
         <v>350</v>
       </c>
-      <c r="P11" s="46" t="n"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" t="n">
         <v>4590840</v>
       </c>
@@ -3798,7 +4008,30 @@
       <c r="H12" t="n">
         <v>350</v>
       </c>
-      <c r="P12" s="46" t="n"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>500</v>
       </c>
@@ -3886,7 +4119,30 @@
       <c r="H14" t="n">
         <v>350</v>
       </c>
-      <c r="P14" s="46" t="n"/>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X14">
         <f t="array" ref="X14">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B14, _xlpm.payments, E14:P14, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -3918,15 +4174,33 @@
       <c r="G15" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="H15" s="62" t="n"/>
-      <c r="I15" s="62" t="n"/>
-      <c r="J15" s="62" t="n"/>
-      <c r="K15" s="62" t="n"/>
-      <c r="L15" s="62" t="n"/>
-      <c r="M15" s="62" t="n"/>
-      <c r="N15" s="62" t="n"/>
-      <c r="O15" s="62" t="n"/>
-      <c r="P15" s="63" t="n"/>
+      <c r="H15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" s="62" t="n"/>
       <c r="X15">
         <f t="array" ref="X15">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B15, _xlpm.payments, E15:P15, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
@@ -3955,7 +4229,30 @@
       <c r="H16" t="n">
         <v>350</v>
       </c>
-      <c r="P16" s="46" t="n"/>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>500</v>
       </c>
@@ -3986,7 +4283,30 @@
       <c r="H17" t="n">
         <v>350</v>
       </c>
-      <c r="P17" s="46" t="n"/>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="n">
         <v>500</v>
       </c>
@@ -4014,8 +4334,33 @@
       <c r="G18" t="n">
         <v>350</v>
       </c>
-      <c r="O18" s="149" t="n"/>
-      <c r="P18" s="156" t="n"/>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>500</v>
       </c>
@@ -4048,8 +4393,33 @@
       <c r="G19" t="n">
         <v>350</v>
       </c>
-      <c r="O19" s="46" t="n"/>
-      <c r="P19" s="46" t="n"/>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>500</v>
       </c>
@@ -4114,7 +4484,30 @@
       <c r="H21" t="n">
         <v>350</v>
       </c>
-      <c r="P21" s="46" t="n"/>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X21">
         <f t="array" ref="X21">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B21, _xlpm.payments, E21:P21, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4142,7 +4535,30 @@
       <c r="H22" t="n">
         <v>350</v>
       </c>
-      <c r="P22" s="46" t="n"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>500</v>
       </c>
@@ -4170,7 +4586,33 @@
       <c r="G23" t="n">
         <v>350</v>
       </c>
-      <c r="P23" s="46" t="n"/>
+      <c r="H23" t="n">
+        <v>350</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X23">
         <f t="array" ref="X23">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B23, _xlpm.payments, E23:P23, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4198,7 +4640,30 @@
       <c r="H24" t="n">
         <v>350</v>
       </c>
-      <c r="P24" s="46" t="n"/>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>500</v>
       </c>
@@ -4232,14 +4697,30 @@
       <c r="H25" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I25" s="62" t="n"/>
-      <c r="J25" s="62" t="n"/>
-      <c r="K25" s="62" t="n"/>
-      <c r="L25" s="62" t="n"/>
-      <c r="M25" s="62" t="n"/>
-      <c r="N25" s="62" t="n"/>
-      <c r="O25" s="62" t="n"/>
-      <c r="P25" s="63" t="n"/>
+      <c r="I25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>500</v>
       </c>
@@ -4276,7 +4757,30 @@
       <c r="H26" s="50" t="n">
         <v>350</v>
       </c>
-      <c r="P26" s="46" t="n"/>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>500</v>
       </c>
@@ -4337,7 +4841,30 @@
       <c r="H28" t="n">
         <v>350</v>
       </c>
-      <c r="P28" s="46" t="n"/>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>500</v>
       </c>
@@ -4371,8 +4898,30 @@
       <c r="H29" t="n">
         <v>350</v>
       </c>
-      <c r="O29" s="50" t="n"/>
-      <c r="P29" s="46" t="n"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>500</v>
       </c>
@@ -4419,12 +4968,24 @@
       <c r="J30" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="K30" s="62" t="n"/>
-      <c r="L30" s="62" t="n"/>
-      <c r="M30" s="62" t="n"/>
-      <c r="N30" s="62" t="n"/>
-      <c r="O30" s="150" t="n"/>
-      <c r="P30" s="157" t="n"/>
+      <c r="K30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>500</v>
       </c>
@@ -4456,8 +5017,30 @@
       <c r="H31" t="n">
         <v>350</v>
       </c>
-      <c r="O31" s="149" t="n"/>
-      <c r="P31" s="156" t="n"/>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="X31">
         <f t="array" ref="X31">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B31, _xlpm.payments, E31:P31, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4485,7 +5068,30 @@
       <c r="H32" t="n">
         <v>350</v>
       </c>
-      <c r="P32" s="46" t="n"/>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>500</v>
       </c>
@@ -4521,7 +5127,30 @@
       <c r="H33" t="n">
         <v>350</v>
       </c>
-      <c r="P33" s="46" t="n"/>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>500</v>
       </c>
@@ -4588,14 +5217,30 @@
       <c r="H35" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I35" s="62" t="n"/>
-      <c r="J35" s="62" t="n"/>
-      <c r="K35" s="62" t="n"/>
-      <c r="L35" s="62" t="n"/>
-      <c r="M35" s="62" t="n"/>
-      <c r="N35" s="62" t="n"/>
-      <c r="O35" s="62" t="n"/>
-      <c r="P35" s="63" t="n"/>
+      <c r="I35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>500</v>
       </c>
@@ -4627,7 +5272,30 @@
       <c r="H36" t="n">
         <v>350</v>
       </c>
-      <c r="P36" s="46" t="n"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>500</v>
       </c>
@@ -4661,7 +5329,30 @@
       <c r="H37" t="n">
         <v>350</v>
       </c>
-      <c r="P37" s="46" t="n"/>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X37">
         <f t="array" ref="X37">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B37, _xlpm.payments, E37:P37, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4688,7 +5379,36 @@
       <c r="F38" t="n">
         <v>350</v>
       </c>
-      <c r="P38" s="46" t="n"/>
+      <c r="G38" t="n">
+        <v>350</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X38">
         <f t="array" ref="X38">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B38, _xlpm.payments, E38:P38, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4746,14 +5466,30 @@
       <c r="H40" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I40" s="62" t="n"/>
-      <c r="J40" s="62" t="n"/>
-      <c r="K40" s="62" t="n"/>
-      <c r="L40" s="62" t="n"/>
-      <c r="M40" s="62" t="n"/>
-      <c r="N40" s="62" t="n"/>
-      <c r="O40" s="62" t="n"/>
-      <c r="P40" s="63" t="n"/>
+      <c r="I40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>500</v>
       </c>
@@ -4805,8 +5541,12 @@
       <c r="N41" t="n">
         <v>30</v>
       </c>
-      <c r="O41" s="50" t="n"/>
-      <c r="P41" s="46" t="n"/>
+      <c r="O41" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>500</v>
       </c>
@@ -4837,7 +5577,30 @@
       <c r="H42" t="n">
         <v>350</v>
       </c>
-      <c r="P42" s="46" t="n"/>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X42">
         <f t="array" ref="X42">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B42, _xlpm.payments, E42:P42, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4865,7 +5628,30 @@
       <c r="H43" t="n">
         <v>350</v>
       </c>
-      <c r="P43" s="46" t="n"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X43">
         <f t="array" ref="X43">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B43, _xlpm.payments, E43:P43, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4893,7 +5679,30 @@
       <c r="H44" t="n">
         <v>350</v>
       </c>
-      <c r="P44" s="46" t="n"/>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>500</v>
       </c>
@@ -4930,14 +5739,30 @@
       <c r="H45" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I45" s="62" t="n"/>
-      <c r="J45" s="62" t="n"/>
-      <c r="K45" s="62" t="n"/>
-      <c r="L45" s="62" t="n"/>
-      <c r="M45" s="62" t="n"/>
-      <c r="N45" s="62" t="n"/>
-      <c r="O45" s="62" t="n"/>
-      <c r="P45" s="63" t="n"/>
+      <c r="I45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>500</v>
       </c>
@@ -4969,7 +5794,30 @@
       <c r="H46" t="n">
         <v>350</v>
       </c>
-      <c r="P46" s="46" t="n"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" s="50" t="n">
         <v>500</v>
       </c>
@@ -5003,7 +5851,30 @@
       <c r="H47" t="n">
         <v>350</v>
       </c>
-      <c r="P47" s="46" t="n"/>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>500</v>
       </c>
@@ -5099,7 +5970,30 @@
       <c r="H49" t="n">
         <v>350</v>
       </c>
-      <c r="P49" s="46" t="n"/>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>500</v>
       </c>
@@ -5134,15 +6028,33 @@
       <c r="G50" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="H50" s="62" t="n"/>
-      <c r="I50" s="62" t="n"/>
-      <c r="J50" s="62" t="n"/>
-      <c r="K50" s="62" t="n"/>
-      <c r="L50" s="62" t="n"/>
-      <c r="M50" s="62" t="n"/>
-      <c r="N50" s="62" t="n"/>
-      <c r="O50" s="62" t="n"/>
-      <c r="P50" s="63" t="n"/>
+      <c r="H50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>הו"ק ב29 לכל חודש</t>
@@ -5178,8 +6090,30 @@
       <c r="H51" t="n">
         <v>350</v>
       </c>
-      <c r="O51" s="149" t="n"/>
-      <c r="P51" s="156" t="n"/>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>חוב נוב + דצ +ינו 30X3 שקל</t>
@@ -5220,7 +6154,30 @@
       <c r="H52" t="n">
         <v>350</v>
       </c>
-      <c r="P52" s="46" t="n"/>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="S52" t="n">
         <v>4691410</v>
       </c>
@@ -5251,7 +6208,30 @@
       <c r="H53" t="n">
         <v>350</v>
       </c>
-      <c r="P53" s="46" t="n"/>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>500</v>
       </c>
@@ -5277,16 +6257,36 @@
       <c r="F54" s="53" t="n">
         <v>350</v>
       </c>
-      <c r="G54" s="53" t="n"/>
-      <c r="H54" s="53" t="n"/>
-      <c r="I54" s="53" t="n"/>
-      <c r="J54" s="53" t="n"/>
-      <c r="K54" s="53" t="n"/>
-      <c r="L54" s="53" t="n"/>
-      <c r="M54" s="53" t="n"/>
-      <c r="N54" s="53" t="n"/>
-      <c r="O54" s="152" t="n"/>
-      <c r="P54" s="172" t="n"/>
+      <c r="G54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="172" t="n">
+        <v>0</v>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>הו"ק ב28 לכל חודש</t>
@@ -5322,7 +6322,30 @@
       <c r="H55" t="n">
         <v>350</v>
       </c>
-      <c r="P55" s="46" t="n"/>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="S55" t="n">
         <v>4763312</v>
       </c>
@@ -5358,7 +6381,30 @@
       <c r="H56" t="n">
         <v>350</v>
       </c>
-      <c r="P56" s="46" t="n"/>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>500</v>
       </c>
@@ -5394,7 +6440,30 @@
       <c r="H57" t="n">
         <v>350</v>
       </c>
-      <c r="P57" s="46" t="n"/>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>500</v>
       </c>
@@ -5428,7 +6497,30 @@
       <c r="H58" t="n">
         <v>350</v>
       </c>
-      <c r="P58" s="46" t="n"/>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X58">
         <f t="array" ref="X58">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B58, _xlpm.payments, E58:P58, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5453,7 +6545,33 @@
       <c r="G59" t="n">
         <v>350</v>
       </c>
-      <c r="P59" s="156" t="n"/>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="S59" t="n">
         <v>4660306</v>
       </c>
@@ -5487,14 +6605,30 @@
       <c r="H60" s="62" t="n">
         <v>350</v>
       </c>
-      <c r="I60" s="62" t="n"/>
-      <c r="J60" s="62" t="n"/>
-      <c r="K60" s="62" t="n"/>
-      <c r="L60" s="62" t="n"/>
-      <c r="M60" s="62" t="n"/>
-      <c r="N60" s="62" t="n"/>
-      <c r="O60" s="62" t="n"/>
-      <c r="P60" s="63" t="n"/>
+      <c r="I60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="63" t="n">
+        <v>0</v>
+      </c>
       <c r="S60" s="61" t="inlineStr">
         <is>
           <t>חרזי / עינב</t>
@@ -5532,14 +6666,30 @@
       <c r="H61" s="53" t="n">
         <v>350</v>
       </c>
-      <c r="I61" s="53" t="n"/>
-      <c r="J61" s="53" t="n"/>
-      <c r="K61" s="53" t="n"/>
-      <c r="L61" s="53" t="n"/>
-      <c r="M61" s="53" t="n"/>
-      <c r="N61" s="53" t="n"/>
-      <c r="O61" s="53" t="n"/>
-      <c r="P61" s="55" t="n"/>
+      <c r="I61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>500</v>
       </c>
@@ -19160,9 +20310,6 @@
           <t>הפקדת שיק</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/האגמית7_כספים_2026.xlsx
+++ b/האגמית7_כספים_2026.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קופה קטנה" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חוב דירה 13" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פירוט_גביה_4" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="פירוט_הוצאות_4" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -4335,7 +4336,7 @@
         <v>350</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -6983,7 +6984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" bestFit="1" customWidth="1" style="177" min="1" max="1"/>
@@ -7095,15 +7096,33 @@
       <c r="D2" s="246" t="n">
         <v>7500</v>
       </c>
-      <c r="E2" s="246" t="n"/>
-      <c r="F2" s="246" t="n"/>
-      <c r="G2" s="246" t="n"/>
-      <c r="H2" s="246" t="n"/>
-      <c r="I2" s="246" t="n"/>
-      <c r="J2" s="246" t="n"/>
-      <c r="K2" s="246" t="n"/>
-      <c r="L2" s="246" t="n"/>
-      <c r="M2" s="246" t="n"/>
+      <c r="E2" s="246" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7128,15 +7147,33 @@
       <c r="D3" s="246" t="n">
         <v>4549.48</v>
       </c>
-      <c r="E3" s="246" t="n"/>
-      <c r="F3" s="246" t="n"/>
-      <c r="G3" s="246" t="n"/>
-      <c r="H3" s="246" t="n"/>
-      <c r="I3" s="246" t="n"/>
-      <c r="J3" s="246" t="n"/>
-      <c r="K3" s="246" t="n"/>
-      <c r="L3" s="246" t="n"/>
-      <c r="M3" s="246" t="n"/>
+      <c r="E3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7161,15 +7198,33 @@
       <c r="D4" s="246" t="n">
         <v>3233.77</v>
       </c>
-      <c r="E4" s="246" t="n"/>
-      <c r="F4" s="246" t="n"/>
-      <c r="G4" s="246" t="n"/>
-      <c r="H4" s="246" t="n"/>
-      <c r="I4" s="246" t="n"/>
-      <c r="J4" s="246" t="n"/>
-      <c r="K4" s="246" t="n"/>
-      <c r="L4" s="246" t="n"/>
-      <c r="M4" s="246" t="n"/>
+      <c r="E4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7197,14 +7252,30 @@
       <c r="E5" s="246" t="n">
         <v>900</v>
       </c>
-      <c r="F5" s="246" t="n"/>
-      <c r="G5" s="246" t="n"/>
-      <c r="H5" s="246" t="n"/>
-      <c r="I5" s="246" t="n"/>
-      <c r="J5" s="246" t="n"/>
-      <c r="K5" s="246" t="n"/>
-      <c r="L5" s="246" t="n"/>
-      <c r="M5" s="246" t="n"/>
+      <c r="F5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7229,15 +7300,33 @@
       <c r="D6" s="246" t="n">
         <v>979</v>
       </c>
-      <c r="E6" s="246" t="n"/>
-      <c r="F6" s="246" t="n"/>
-      <c r="G6" s="246" t="n"/>
-      <c r="H6" s="246" t="n"/>
-      <c r="I6" s="246" t="n"/>
-      <c r="J6" s="246" t="n"/>
-      <c r="K6" s="246" t="n"/>
-      <c r="L6" s="246" t="n"/>
-      <c r="M6" s="246" t="n"/>
+      <c r="E6" s="246" t="n">
+        <v>981</v>
+      </c>
+      <c r="F6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7262,15 +7351,33 @@
       <c r="D7" s="246" t="n">
         <v>780.11</v>
       </c>
-      <c r="E7" s="246" t="n"/>
-      <c r="F7" s="246" t="n"/>
-      <c r="G7" s="246" t="n"/>
-      <c r="H7" s="246" t="n"/>
-      <c r="I7" s="246" t="n"/>
-      <c r="J7" s="246" t="n"/>
-      <c r="K7" s="246" t="n"/>
-      <c r="L7" s="246" t="n"/>
-      <c r="M7" s="246" t="n"/>
+      <c r="E7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7295,15 +7402,33 @@
       <c r="D8" s="246" t="n">
         <v>90.77</v>
       </c>
-      <c r="E8" s="246" t="n"/>
-      <c r="F8" s="246" t="n"/>
-      <c r="G8" s="246" t="n"/>
-      <c r="H8" s="246" t="n"/>
-      <c r="I8" s="246" t="n"/>
-      <c r="J8" s="246" t="n"/>
-      <c r="K8" s="246" t="n"/>
-      <c r="L8" s="246" t="n"/>
-      <c r="M8" s="246" t="n"/>
+      <c r="E8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7323,21 +7448,38 @@
         <v>0</v>
       </c>
       <c r="C9" s="246" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="246">
-        <f>77+74.25</f>
-        <v/>
-      </c>
-      <c r="E9" s="246" t="n"/>
-      <c r="F9" s="246" t="n"/>
-      <c r="G9" s="246" t="n"/>
-      <c r="H9" s="246" t="n"/>
-      <c r="I9" s="246" t="n"/>
-      <c r="J9" s="246" t="n"/>
-      <c r="K9" s="246" t="n"/>
-      <c r="L9" s="246" t="n"/>
-      <c r="M9" s="246" t="n"/>
+        <v>48.38</v>
+      </c>
+      <c r="D9" s="246" t="n">
+        <v>77</v>
+      </c>
+      <c r="E9" s="246" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7359,19 +7501,36 @@
       <c r="C10" s="246" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="246">
-        <f>24.57+24.57</f>
-        <v/>
-      </c>
-      <c r="E10" s="246" t="n"/>
-      <c r="F10" s="246" t="n"/>
-      <c r="G10" s="246" t="n"/>
-      <c r="H10" s="246" t="n"/>
-      <c r="I10" s="246" t="n"/>
-      <c r="J10" s="246" t="n"/>
-      <c r="K10" s="246" t="n"/>
-      <c r="L10" s="246" t="n"/>
-      <c r="M10" s="246" t="n"/>
+      <c r="D10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7396,15 +7555,33 @@
       <c r="D11" s="246" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="246" t="n"/>
-      <c r="F11" s="246" t="n"/>
-      <c r="G11" s="246" t="n"/>
-      <c r="H11" s="246" t="n"/>
-      <c r="I11" s="246" t="n"/>
-      <c r="J11" s="246" t="n"/>
-      <c r="K11" s="246" t="n"/>
-      <c r="L11" s="246" t="n"/>
-      <c r="M11" s="246" t="n"/>
+      <c r="E11" s="246" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="246" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7429,15 +7606,33 @@
       <c r="D12" s="249" t="n">
         <v>24.75</v>
       </c>
-      <c r="E12" s="249" t="n"/>
-      <c r="F12" s="249" t="n"/>
-      <c r="G12" s="249" t="n"/>
-      <c r="H12" s="249" t="n"/>
-      <c r="I12" s="249" t="n"/>
-      <c r="J12" s="249" t="n"/>
-      <c r="K12" s="249" t="n"/>
-      <c r="L12" s="249" t="n"/>
-      <c r="M12" s="249" t="n"/>
+      <c r="E12" s="249" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="249" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
         <v/>
@@ -7456,22 +7651,39 @@
       <c r="B13" s="249" t="n">
         <v>606</v>
       </c>
-      <c r="C13" s="249">
-        <f>500+700+48.38+177+665+650+350</f>
-        <v/>
+      <c r="C13" s="249" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="249" t="n">
         <v>6500</v>
       </c>
-      <c r="E13" s="249" t="n"/>
-      <c r="F13" s="249" t="n"/>
-      <c r="G13" s="249" t="n"/>
-      <c r="H13" s="249" t="n"/>
-      <c r="I13" s="249" t="n"/>
-      <c r="J13" s="249" t="n"/>
-      <c r="K13" s="249" t="n"/>
-      <c r="L13" s="249" t="n"/>
-      <c r="M13" s="249" t="n"/>
+      <c r="E13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="249" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" s="247" t="n"/>
       <c r="O13" s="248" t="n"/>
     </row>
@@ -7481,53 +7693,41 @@
           <t>קופה קטנה</t>
         </is>
       </c>
-      <c r="B14" s="249">
-        <f>'קופה קטנה'!B43</f>
-        <v/>
-      </c>
-      <c r="C14" s="249">
-        <f>'קופה קטנה'!C43</f>
-        <v/>
-      </c>
-      <c r="D14" s="249">
-        <f>'קופה קטנה'!D43</f>
-        <v/>
-      </c>
-      <c r="E14" s="249">
-        <f>'קופה קטנה'!E43</f>
-        <v/>
-      </c>
-      <c r="F14" s="249">
-        <f>'קופה קטנה'!F43</f>
-        <v/>
-      </c>
-      <c r="G14" s="249">
-        <f>'קופה קטנה'!G43</f>
-        <v/>
-      </c>
-      <c r="H14" s="249">
-        <f>'קופה קטנה'!H43</f>
-        <v/>
-      </c>
-      <c r="I14" s="249">
-        <f>'קופה קטנה'!I43</f>
-        <v/>
-      </c>
-      <c r="J14" s="249">
-        <f>'קופה קטנה'!J43</f>
-        <v/>
-      </c>
-      <c r="K14" s="249">
-        <f>'קופה קטנה'!K43</f>
-        <v/>
-      </c>
-      <c r="L14" s="249">
-        <f>'קופה קטנה'!L43</f>
-        <v/>
-      </c>
-      <c r="M14" s="249">
-        <f>'קופה קטנה'!M43</f>
-        <v/>
+      <c r="B14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="249" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="249" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="247" t="n"/>
       <c r="O14" s="248" t="n"/>
@@ -7555,53 +7755,41 @@
           <t>הוצאות שוטף</t>
         </is>
       </c>
-      <c r="B16" s="250">
-        <f>SUM(B2:B13)</f>
-        <v/>
-      </c>
-      <c r="C16" s="250">
-        <f>SUM(C2:C13)</f>
-        <v/>
-      </c>
-      <c r="D16" s="250">
-        <f>SUM(D2:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="250">
-        <f>SUM(E2:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="250">
-        <f>SUM(F2:F13)</f>
-        <v/>
-      </c>
-      <c r="G16" s="250">
-        <f>SUM(G2:G13)</f>
-        <v/>
-      </c>
-      <c r="H16" s="250">
-        <f>SUM(H2:H13)</f>
-        <v/>
-      </c>
-      <c r="I16" s="250">
-        <f>SUM(I2:I13)</f>
-        <v/>
-      </c>
-      <c r="J16" s="250">
-        <f>SUM(J2:J13)</f>
-        <v/>
-      </c>
-      <c r="K16" s="250">
-        <f>SUM(K2:K13)</f>
-        <v/>
-      </c>
-      <c r="L16" s="250">
-        <f>SUM(L2:L13)</f>
-        <v/>
-      </c>
-      <c r="M16" s="250">
-        <f>SUM(M2:M13)</f>
-        <v/>
+      <c r="B16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="250" t="n">
+        <v>0</v>
       </c>
       <c r="N16" s="251">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
@@ -7618,53 +7806,41 @@
           <t>הוצאות לא שוטף</t>
         </is>
       </c>
-      <c r="B17" s="250">
-        <f>SUM(B14)</f>
-        <v/>
-      </c>
-      <c r="C17" s="250">
-        <f>SUM(C14)</f>
-        <v/>
-      </c>
-      <c r="D17" s="250">
-        <f>SUM(D14)</f>
-        <v/>
-      </c>
-      <c r="E17" s="250">
-        <f>SUM(E14)</f>
-        <v/>
-      </c>
-      <c r="F17" s="250">
-        <f>SUM(F14)</f>
-        <v/>
-      </c>
-      <c r="G17" s="250">
-        <f>SUM(G14)</f>
-        <v/>
-      </c>
-      <c r="H17" s="250">
-        <f>SUM(H14)</f>
-        <v/>
-      </c>
-      <c r="I17" s="250">
-        <f>SUM(I14)</f>
-        <v/>
-      </c>
-      <c r="J17" s="250">
-        <f>SUM(J14)</f>
-        <v/>
-      </c>
-      <c r="K17" s="250">
-        <f>SUM(K14)</f>
-        <v/>
-      </c>
-      <c r="L17" s="250">
-        <f>SUM(L14)</f>
-        <v/>
-      </c>
-      <c r="M17" s="250">
-        <f>SUM(M14)</f>
-        <v/>
+      <c r="B17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="250" t="n">
+        <v>0</v>
       </c>
       <c r="N17" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
@@ -7681,53 +7857,41 @@
           <t>הוצאות סה"כ</t>
         </is>
       </c>
-      <c r="B18" s="250">
-        <f>SUM(B16:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="250">
-        <f>SUM(C16:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="250">
-        <f>SUM(D16:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="250">
-        <f>SUM(E16:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="250">
-        <f>SUM(F16:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="250">
-        <f>SUM(G16:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="250">
-        <f>SUM(H16:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="250">
-        <f>SUM(I16:I17)</f>
-        <v/>
-      </c>
-      <c r="J18" s="250">
-        <f>SUM(J16:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="250">
-        <f>SUM(K16:K17)</f>
-        <v/>
-      </c>
-      <c r="L18" s="250">
-        <f>SUM(L16:L17)</f>
-        <v/>
-      </c>
-      <c r="M18" s="250">
-        <f>SUM(M16:M17)</f>
-        <v/>
+      <c r="B18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="250" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
@@ -7744,53 +7908,41 @@
           <t>הכנסות שוטף</t>
         </is>
       </c>
-      <c r="B19" s="246">
-        <f>'גביה 2026'!E62</f>
-        <v/>
-      </c>
-      <c r="C19" s="246">
-        <f>'גביה 2026'!F62</f>
-        <v/>
-      </c>
-      <c r="D19" s="246">
-        <f>'גביה 2026'!G62</f>
-        <v/>
-      </c>
-      <c r="E19" s="246">
-        <f>'גביה 2026'!H62</f>
-        <v/>
-      </c>
-      <c r="F19" s="246">
-        <f>'גביה 2026'!I62</f>
-        <v/>
-      </c>
-      <c r="G19" s="246">
-        <f>'גביה 2026'!J62</f>
-        <v/>
-      </c>
-      <c r="H19" s="246">
-        <f>'גביה 2026'!K62</f>
-        <v/>
-      </c>
-      <c r="I19" s="246">
-        <f>'גביה 2026'!L62</f>
-        <v/>
-      </c>
-      <c r="J19" s="246">
-        <f>'גביה 2026'!M62</f>
-        <v/>
-      </c>
-      <c r="K19" s="246">
-        <f>'גביה 2026'!N62</f>
-        <v/>
-      </c>
-      <c r="L19" s="246">
-        <f>'גביה 2026'!O62</f>
-        <v/>
-      </c>
-      <c r="M19" s="246">
-        <f>'גביה 2026'!P62</f>
-        <v/>
+      <c r="B19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="246" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
@@ -7807,53 +7959,41 @@
           <t>יחס שוטף הכנסות/הוצאות</t>
         </is>
       </c>
-      <c r="B20" s="195">
-        <f>B16/B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="195">
-        <f>C16/C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="195">
-        <f>D16/D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="195">
-        <f>E16/E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="195">
-        <f>F16/F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="195">
-        <f>G16/G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="195">
-        <f>H16/H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="195">
-        <f>I16/I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="195">
-        <f>J16/J19</f>
-        <v/>
-      </c>
-      <c r="K20" s="195">
-        <f>K16/K19</f>
-        <v/>
-      </c>
-      <c r="L20" s="195">
-        <f>L16/L19</f>
-        <v/>
-      </c>
-      <c r="M20" s="195">
-        <f>M16/M19</f>
-        <v/>
+      <c r="B20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="195" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="247">
         <f>AVERAGE(Table2[[#This Row],[ינואר 25]:[דצמבר 25]])</f>
@@ -7864,29 +8004,58 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23" ht="57.75" customHeight="1" s="177">
       <c r="A23" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
       </c>
-      <c r="B23" s="176" t="inlineStr">
-        <is>
-          <t>בדק מעליות
-גינון 600 שקל דשן</t>
-        </is>
-      </c>
-      <c r="C23" s="176" t="inlineStr">
-        <is>
-          <t>סידור אבנים משתלבות + משלוח סטרימר נובולה + אנטילופה + גופי תאורה 2 + כבל 20 מטר + צילינדר + ספק מנועל + ממסר למחסום</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>שיפוץ חדרי מדרגות</t>
-        </is>
-      </c>
-    </row>
+      <c r="B23" s="176" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="159" t="inlineStr">
         <is>
@@ -7938,6 +8107,24 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <conditionalFormatting sqref="B20:M20">
     <cfRule type="colorScale" priority="1">
@@ -20241,7 +20428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21895,6 +22082,367 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>350</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>לא ידוע</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>לא זוהה</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>לא ידוע</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>הפקדת שיק</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Entity_Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Original_Desc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Original_Ext_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>מסלול בנק</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>בנק</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>מסלול מורחב</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>עמלות בנק</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>בנק</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>עמל.ערוץ יש 16</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>סכום החיוב מייצג את מספר התנועות שבוצעו בערוץ ישיר/פקיד.  מספר התנועות מופיע בסמוך למלל.  סכום העמלה לפעולה הינו כפי המופיע בתעריף העמלות ליחיד/תאגיד ובהתאם להטבות הקיימות ללקוח דהיינו סכום חיוב = מספר תנועות ערוץ פקיד/ישיר כפול תעריף העמלה בחשבון הלקוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-77</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Novula - מסך טלויזיה</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>נובולה</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>נובולה בע"מ-י</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>יניב אחזקות</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>גל אנתבי</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>הוראת קבע</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>העברה ל: גל אנתבי 20-505-00159972 תאריך סיום: 09.12.2027 ניקיון האגמית 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-981</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ביטוח</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ש.שלמה חברה</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ש.שלמה חברה-י</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-239</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>הוצאה (העברה)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>אבישי שורץ 11-076-006640178 צבע</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>הע. אינטרנט</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>העברה אל: אבישי שורץ 11-076-006640178 צבע</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-69</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>הוצאה (העברה)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>אבישי שורץ 11-076-006640178 מברשת פלדה דגל</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>הע. אינטרנט</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>העברה אל: אבישי שורץ 11-076-006640178 מברשת פלדה דגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-2006</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>הוצאה (העברה)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>יעקב אלישע 12-719-000272874 האגמית 7 חיטוי מאגרים</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>העברה דיגיטל</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>העברה אל: יעקב אלישע 12-719-000272874 האגמית 7 חיטוי מאגרים</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>הוצאה (העברה)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>אבישי שורץ 11-076-006640178 דגל יום עצמאות</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>הע. אינטרנט</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>העברה אל: אבישי שורץ 11-076-006640178 דגל יום עצמאות</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>הוצאה (העברה)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>יניב מאיר 20-505-000159972 האגמית 7 דגלים</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>הע. אינטרנט</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>העברה אל: יניב מאיר 20-505-000159972 האגמית 7 דגלים</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/האגמית7_כספים_2026.xlsx
+++ b/האגמית7_כספים_2026.xlsx
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="246" t="n">
-        <v>48.38</v>
+        <v>0</v>
       </c>
       <c r="D9" s="246" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="E9" s="246" t="n">
         <v>77</v>

--- a/האגמית7_כספים_2026.xlsx
+++ b/האגמית7_כספים_2026.xlsx
@@ -3478,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="S2" s="62" t="n"/>
       <c r="X2">
@@ -3510,10 +3510,10 @@
         <v>350</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -3534,6 +3534,9 @@
         <v>0</v>
       </c>
       <c r="P3" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="X3">
@@ -3644,6 +3647,9 @@
       <c r="P5" s="63" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" s="62" t="n"/>
       <c r="X5">
         <f t="array" ref="X5">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B5, _xlpm.payments, E5:P5, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
@@ -3873,6 +3879,9 @@
       <c r="P9" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
       <c r="X9">
         <f t="array" ref="X9">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B9, _xlpm.payments, E9:P9, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -3925,6 +3934,9 @@
         <v>0</v>
       </c>
       <c r="P10" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="S10" s="62" t="n"/>
@@ -3979,6 +3991,9 @@
       <c r="P11" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" t="n">
         <v>4590840</v>
       </c>
@@ -4144,6 +4159,9 @@
       <c r="P14" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
       <c r="X14">
         <f t="array" ref="X14">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B14, _xlpm.payments, E14:P14, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4176,10 +4194,10 @@
         <v>350</v>
       </c>
       <c r="H15" s="62" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I15" s="62" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="J15" s="62" t="n">
         <v>0</v>
@@ -4200,6 +4218,9 @@
         <v>0</v>
       </c>
       <c r="P15" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="62" t="n"/>
@@ -4442,18 +4463,42 @@
         </is>
       </c>
       <c r="D20" s="62" t="n"/>
-      <c r="E20" s="169" t="n"/>
-      <c r="F20" s="66" t="n"/>
-      <c r="G20" s="66" t="n"/>
-      <c r="H20" s="66" t="n"/>
-      <c r="I20" s="66" t="n"/>
-      <c r="J20" s="66" t="n"/>
-      <c r="K20" s="66" t="n"/>
-      <c r="L20" s="66" t="n"/>
-      <c r="M20" s="66" t="n"/>
-      <c r="N20" s="66" t="n"/>
-      <c r="O20" s="66" t="n"/>
-      <c r="P20" s="67" t="n"/>
+      <c r="E20" s="169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>350</v>
       </c>
@@ -4509,6 +4554,9 @@
       <c r="P21" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
       <c r="X21">
         <f t="array" ref="X21">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B21, _xlpm.payments, E21:P21, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4614,6 +4662,9 @@
       <c r="P23" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q23" t="n">
+        <v>200</v>
+      </c>
       <c r="X23">
         <f t="array" ref="X23">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B23, _xlpm.payments, E23:P23, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -4800,18 +4851,42 @@
           <t>שוורץ</t>
         </is>
       </c>
-      <c r="E27" s="170" t="n"/>
-      <c r="F27" s="48" t="n"/>
-      <c r="G27" s="48" t="n"/>
-      <c r="H27" s="48" t="n"/>
-      <c r="I27" s="48" t="n"/>
-      <c r="J27" s="48" t="n"/>
-      <c r="K27" s="48" t="n"/>
-      <c r="L27" s="48" t="n"/>
-      <c r="M27" s="48" t="n"/>
-      <c r="N27" s="48" t="n"/>
-      <c r="O27" s="48" t="n"/>
-      <c r="P27" s="49" t="n"/>
+      <c r="E27" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>500</v>
       </c>
@@ -5042,6 +5117,9 @@
       <c r="P31" s="156" t="n">
         <v>0</v>
       </c>
+      <c r="Q31" t="n">
+        <v>500</v>
+      </c>
       <c r="X31">
         <f t="array" ref="X31">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B31, _xlpm.payments, E31:P31, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5173,18 +5251,42 @@
           <t>וילצר</t>
         </is>
       </c>
-      <c r="E34" s="170" t="n"/>
-      <c r="F34" s="48" t="n"/>
-      <c r="G34" s="48" t="n"/>
-      <c r="H34" s="48" t="n"/>
-      <c r="I34" s="48" t="n"/>
-      <c r="J34" s="48" t="n"/>
-      <c r="K34" s="48" t="n"/>
-      <c r="L34" s="48" t="n"/>
-      <c r="M34" s="48" t="n"/>
-      <c r="N34" s="48" t="n"/>
-      <c r="O34" s="48" t="n"/>
-      <c r="P34" s="49" t="n"/>
+      <c r="E34" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>500</v>
       </c>
@@ -5354,6 +5456,9 @@
       <c r="P37" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
       <c r="X37">
         <f t="array" ref="X37">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B37, _xlpm.payments, E37:P37, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5410,6 +5515,9 @@
       <c r="P38" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
       <c r="X38">
         <f t="array" ref="X38">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B38, _xlpm.payments, E38:P38, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5425,18 +5533,45 @@
           <t>ברכה</t>
         </is>
       </c>
-      <c r="E39" s="170" t="n"/>
-      <c r="F39" s="48" t="n"/>
-      <c r="G39" s="48" t="n"/>
-      <c r="H39" s="48" t="n"/>
-      <c r="I39" s="48" t="n"/>
-      <c r="J39" s="48" t="n"/>
-      <c r="K39" s="48" t="n"/>
-      <c r="L39" s="48" t="n"/>
-      <c r="M39" s="48" t="n"/>
-      <c r="N39" s="48" t="n"/>
-      <c r="O39" s="48" t="n"/>
-      <c r="P39" s="49" t="n"/>
+      <c r="E39" s="170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
       <c r="X39">
         <f t="array" ref="X39">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B39, _xlpm.payments, E39:P39, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5602,6 +5737,9 @@
       <c r="P42" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
       <c r="X42">
         <f t="array" ref="X42">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B42, _xlpm.payments, E42:P42, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -5653,6 +5791,9 @@
       <c r="P43" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
       <c r="X43">
         <f t="array" ref="X43">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B43, _xlpm.payments, E43:P43, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -6056,6 +6197,9 @@
       <c r="P50" s="63" t="n">
         <v>0</v>
       </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>הו"ק ב29 לכל חודש</t>
@@ -6115,6 +6259,9 @@
       <c r="P51" s="156" t="n">
         <v>0</v>
       </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>חוב נוב + דצ +ינו 30X3 שקל</t>
@@ -6179,6 +6326,9 @@
       <c r="P52" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
       <c r="S52" t="n">
         <v>4691410</v>
       </c>
@@ -6288,6 +6438,9 @@
       <c r="P54" s="172" t="n">
         <v>0</v>
       </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>הו"ק ב28 לכל חודש</t>
@@ -6347,6 +6500,9 @@
       <c r="P55" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
       <c r="S55" t="n">
         <v>4763312</v>
       </c>
@@ -6522,6 +6678,9 @@
       <c r="P58" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
       <c r="X58">
         <f t="array" ref="X58">_xlfn.LET(_xlpm.exclude_list, {19,26,33,38}, _xlpm.current_month_idx, MONTH(TODAY()), _xlpm.month_names, {"ינואר","פברואר","מרץ","אפריל","מאי","יוני","יולי","אוגוסט","ספטמבר","אוקטובר","נובמבר","דצמבר"}, _xlpm.target, 350, _xlpm.apartment, B58, _xlpm.payments, E58:P58, IF(ISNUMBER(MATCH(_xlpm.apartment, _xlpm.exclude_list, 0)), "", _xlfn.LET(_xlpm.debt_list, _xlfn.MAP(_xlfn.SEQUENCE(1, 12), _xlpm.month_names, _xlpm.payments, _xlfn.LAMBDA(_xlpm.idx,_xlpm.m_name,_xlpm.p_val, IF(_xlpm.idx &gt; _xlpm.current_month_idx, "", IF(OR(ISBLANK(_xlpm.p_val), _xlpm.p_val = ""), _xlpm.m_name &amp; " (חוב " &amp; _xlpm.target &amp; ")", IF(_xlpm.p_val &lt; _xlpm.target, _xlpm.m_name &amp; " (חוב " &amp; (_xlpm.target - _xlpm.p_val) &amp; ")", ""))))), _xlpm.summary, _xlfn.TEXTJOIN(", ", TRUE, _xlpm.debt_list), IF(_xlpm.summary &lt;&gt; "", "דירה " &amp; _xlpm.apartment &amp; " - " &amp; _xlpm.summary, ""))))</f>
         <v/>
@@ -6547,7 +6706,7 @@
         <v>350</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -6571,6 +6730,9 @@
         <v>0</v>
       </c>
       <c r="P59" s="156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
@@ -6628,6 +6790,9 @@
         <v>0</v>
       </c>
       <c r="P60" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="S60" s="61" t="inlineStr">
@@ -6984,7 +7149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.7109375" bestFit="1" customWidth="1" style="177" min="1" max="1"/>
@@ -7199,7 +7364,7 @@
         <v>3233.77</v>
       </c>
       <c r="E4" s="246" t="n">
-        <v>0</v>
+        <v>3353.66</v>
       </c>
       <c r="F4" s="246" t="n">
         <v>0</v>
@@ -7403,7 +7568,7 @@
         <v>90.77</v>
       </c>
       <c r="E8" s="246" t="n">
-        <v>0</v>
+        <v>90.77</v>
       </c>
       <c r="F8" s="246" t="n">
         <v>0</v>
@@ -8004,8 +8169,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="57.75" customHeight="1" s="177">
       <c r="A23" t="inlineStr">
         <is>
@@ -8049,13 +8212,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="159" t="inlineStr">
         <is>
@@ -8107,24 +8263,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <conditionalFormatting sqref="B20:M20">
     <cfRule type="colorScale" priority="1">
@@ -20428,7 +20566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22109,6 +22247,105 @@
       <c r="F51" t="inlineStr">
         <is>
           <t>הפקדת שיק</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>700</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>הכנסה מדיירים</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>פיליפ אלברט 10-916-004497512 וועד בית אפריל ומאי דירה 2</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>העברה דיגיטל</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>העברה מאת: פיליפ אלברט 10-916-004497512 וועד בית אפריל ומאי דירה 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>350</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>הכנסה מדיירים</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>58</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>אליאס סמעאן 10-877-003268585 תשלום</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>העברה דיגיטל</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>העברה מאת: אליאס סמעאן 10-877-003268585 תשלום</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>700</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>הכנסה מדיירים</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ירין חיים מל 10-882-046518869 ועד בית</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>העברה דיגיטל</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>העברה מאת: ירין חיים מל 10-882-046518869 ועד בית</t>
         </is>
       </c>
     </row>
@@ -22123,7 +22360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22443,6 +22680,56 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-90.77</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>פרטנר</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>חברת פרטנר</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>חברת פרטנר ת-י</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-3353.66</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>חשמל ציבורי</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>חברת החשמל</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>חברת החשמל ל-י</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/האגמית7_כספים_2026.xlsx
+++ b/האגמית7_כספים_2026.xlsx
@@ -4416,7 +4416,7 @@
         <v>350</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
         <v>350</v>
       </c>
       <c r="H50" s="62" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="I50" s="62" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
         <v>4549.48</v>
       </c>
       <c r="E3" s="246" t="n">
-        <v>0</v>
+        <v>4558.28</v>
       </c>
       <c r="F3" s="246" t="n">
         <v>0</v>
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="246" t="n">
-        <v>0</v>
+        <v>24.57</v>
       </c>
       <c r="F10" s="246" t="n">
         <v>0</v>
@@ -20566,7 +20566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22346,6 +22346,72 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>העברה מאת: ירין חיים מל 10-882-046518869 ועד בית</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>350</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>הכנסה מדיירים</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>18</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>לגסה סיטוטאו יטא 12-700-000089393 חודש רביעי</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>בנק הפועלים</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>העברה מאת: לגסה סיטוטאו יטא 12-700-000089393 חודש רביעי</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>350</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>הכנסה מדיירים</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>49</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>תמר ברנר</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>הוראת קבע</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>העברה מאת: תמר ברנר, דן ברנ 10-885-004050720 ועד בית דירה 49</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22730,6 +22796,56 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-24.57</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>בזק</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>בזק-הוראות</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>בזק-הוראות ק-י</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-4558.28</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>קונה מעליות</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>קונה</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>קונה בע"מ-י</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
